--- a/All_Code/Q2/Results/Tables/annual_cost_summary.xlsx
+++ b/All_Code/Q2/Results/Tables/annual_cost_summary.xlsx
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14065827.90394515</v>
+        <v>14797743.36569577</v>
       </c>
       <c r="C2" t="n">
-        <v>42113.25719744057</v>
+        <v>44304.62085537656</v>
       </c>
       <c r="D2" t="n">
         <v>334</v>
@@ -461,10 +461,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1175366.997561327</v>
+        <v>839786.4576860523</v>
       </c>
       <c r="C3" t="n">
-        <v>3519.062866950081</v>
+        <v>2514.330711634887</v>
       </c>
       <c r="D3" t="n">
         <v>334</v>
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15241194.90150647</v>
+        <v>15637529.82338182</v>
       </c>
       <c r="C4" t="n">
-        <v>45632.32006439064</v>
+        <v>46818.95156701144</v>
       </c>
       <c r="D4" t="n">
         <v>334</v>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>307585.8236036318</v>
+        <v>221843.7393478658</v>
       </c>
       <c r="C5" t="n">
-        <v>920.9156395318316</v>
+        <v>664.2028124187598</v>
       </c>
       <c r="D5" t="n">
         <v>334</v>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1909728.333827129</v>
+        <v>2247853.336452647</v>
       </c>
       <c r="C6" t="n">
-        <v>5717.749502476435</v>
+        <v>6730.099809738465</v>
       </c>
       <c r="D6" t="n">
         <v>334</v>
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1557932.105519569</v>
+        <v>2220352.680997587</v>
       </c>
       <c r="C7" t="n">
-        <v>4664.467381795117</v>
+        <v>6647.762517956849</v>
       </c>
       <c r="D7" t="n">
         <v>334</v>
@@ -537,7 +537,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>参数: beta=0.0, M=30, kappa2=0.132917, alpha=0.9；费用不含 eps 与 kappa2 罚项</t>
+          <t>参数: beta=0.25, M=20, kappa2=0.132917, alpha=0.9；费用不含 eps 与 kappa2 罚项</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
